--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CALVO BASKET XIRIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CALVO BASKET XIRIA.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>121.5597</v>
+        <v>116.7077</v>
       </c>
       <c r="E2" t="n">
-        <v>89.8222</v>
+        <v>87.3528</v>
       </c>
       <c r="F2" t="n">
-        <v>31.7375</v>
+        <v>29.3552</v>
       </c>
       <c r="G2" t="n">
         <v>72.1283</v>
@@ -610,13 +610,13 @@
         <v>57.1875</v>
       </c>
       <c r="S2" t="n">
-        <v>16.4454</v>
+        <v>11.5935</v>
       </c>
       <c r="T2" t="n">
-        <v>8.220499999999999</v>
+        <v>5.7506</v>
       </c>
       <c r="U2" t="n">
-        <v>8.225199999999999</v>
+        <v>5.8429</v>
       </c>
       <c r="V2" t="n">
         <v>44.5414</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>29.4954</v>
+        <v>28.1123</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8998</v>
+        <v>16.3106</v>
       </c>
       <c r="F3" t="n">
-        <v>26.5957</v>
+        <v>11.8017</v>
       </c>
       <c r="G3" t="n">
-        <v>21.5234</v>
+        <v>11.557</v>
       </c>
       <c r="H3" t="n">
-        <v>17.1416</v>
+        <v>7.7537</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3819</v>
+        <v>3.8034</v>
       </c>
       <c r="J3" t="n">
-        <v>28.1159</v>
+        <v>30.9502</v>
       </c>
       <c r="K3" t="n">
-        <v>25.7138</v>
+        <v>23.0371</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4021</v>
+        <v>7.9131</v>
       </c>
       <c r="M3" t="n">
-        <v>-6.5924</v>
+        <v>-19.3934</v>
       </c>
       <c r="N3" t="n">
-        <v>-8.5724</v>
+        <v>-15.2832</v>
       </c>
       <c r="O3" t="n">
-        <v>1.98</v>
+        <v>-4.1099</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.638</v>
+        <v>10.184</v>
       </c>
       <c r="Q3" t="n">
-        <v>-43.0866</v>
+        <v>-38.7775</v>
       </c>
       <c r="R3" t="n">
-        <v>35.4485</v>
+        <v>48.9619</v>
       </c>
       <c r="S3" t="n">
-        <v>25.4167</v>
+        <v>3.9158</v>
       </c>
       <c r="T3" t="n">
-        <v>11.6072</v>
+        <v>4.6978</v>
       </c>
       <c r="U3" t="n">
-        <v>13.8091</v>
+        <v>-0.7822</v>
       </c>
       <c r="V3" t="n">
-        <v>-9.806699999999999</v>
+        <v>2.4549</v>
       </c>
       <c r="W3" t="n">
-        <v>6.2631</v>
+        <v>19.4408</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.0697</v>
+        <v>-16.9858</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>23.1593</v>
+        <v>27.2606</v>
       </c>
       <c r="E4" t="n">
-        <v>7.081000000000001</v>
+        <v>9.421099999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>16.0785</v>
+        <v>17.8397</v>
       </c>
       <c r="G4" t="n">
         <v>0.162500000000001</v>
@@ -766,13 +766,13 @@
         <v>49.941</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1871999999999998</v>
+        <v>4.2885</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01939999999999986</v>
+        <v>2.3591</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1679999999999998</v>
+        <v>1.9291</v>
       </c>
       <c r="V4" t="n">
         <v>12.0382</v>
@@ -799,13 +799,13 @@
         <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>22.9783</v>
+        <v>24.7638</v>
       </c>
       <c r="E5" t="n">
-        <v>6.597000000000001</v>
+        <v>4.2561</v>
       </c>
       <c r="F5" t="n">
-        <v>16.3814</v>
+        <v>20.5076</v>
       </c>
       <c r="G5" t="n">
         <v>-3.465100000000001</v>
@@ -844,13 +844,13 @@
         <v>35.2527</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.001899999999999902</v>
+        <v>1.7832</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7171</v>
+        <v>0.3765000000000003</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.7192</v>
+        <v>1.407</v>
       </c>
       <c r="V5" t="n">
         <v>13.7155</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>19.0861</v>
+        <v>16.8635</v>
       </c>
       <c r="E6" t="n">
-        <v>14.1752</v>
+        <v>-3.0986</v>
       </c>
       <c r="F6" t="n">
-        <v>4.910900000000002</v>
+        <v>19.9623</v>
       </c>
       <c r="G6" t="n">
-        <v>11.557</v>
+        <v>21.5234</v>
       </c>
       <c r="H6" t="n">
-        <v>7.7537</v>
+        <v>17.1416</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8034</v>
+        <v>4.3819</v>
       </c>
       <c r="J6" t="n">
-        <v>30.9502</v>
+        <v>28.1159</v>
       </c>
       <c r="K6" t="n">
-        <v>23.0371</v>
+        <v>25.7138</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9131</v>
+        <v>2.4021</v>
       </c>
       <c r="M6" t="n">
-        <v>-19.3934</v>
+        <v>-6.5924</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.2832</v>
+        <v>-8.5724</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.1099</v>
+        <v>1.98</v>
       </c>
       <c r="P6" t="n">
-        <v>10.184</v>
+        <v>-7.638</v>
       </c>
       <c r="Q6" t="n">
-        <v>-38.7775</v>
+        <v>-43.0866</v>
       </c>
       <c r="R6" t="n">
-        <v>48.9619</v>
+        <v>35.4485</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.11</v>
+        <v>12.7846</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5625</v>
+        <v>5.608899999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.6727</v>
+        <v>7.1754</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4549</v>
+        <v>-9.806699999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>19.4408</v>
+        <v>6.2631</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.9858</v>
+        <v>-16.0697</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. TOMIC</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>8.442499999999999</v>
+        <v>16.1842</v>
       </c>
       <c r="E7" t="n">
-        <v>8.4611</v>
+        <v>15.7384</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01870000000000027</v>
+        <v>0.4456000000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4129</v>
+        <v>5.586</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3401</v>
+        <v>2.213999999999998</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7531</v>
+        <v>3.372400000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>8.940999999999999</v>
+        <v>36.9287</v>
       </c>
       <c r="K7" t="n">
-        <v>1.366</v>
+        <v>24.3657</v>
       </c>
       <c r="L7" t="n">
-        <v>7.5749</v>
+        <v>12.5633</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.5281</v>
+        <v>-31.3425</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.7061</v>
+        <v>-22.1516</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8221</v>
+        <v>-9.1907</v>
       </c>
       <c r="P7" t="n">
-        <v>6.4628</v>
+        <v>20.9557</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3501</v>
+        <v>-31.3355</v>
       </c>
       <c r="R7" t="n">
-        <v>8.812899999999999</v>
+        <v>52.2912</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2614</v>
+        <v>-1.9213</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5951</v>
+        <v>1.5845</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3337</v>
+        <v>-3.5053</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.6948</v>
+        <v>-8.437100000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2754</v>
+        <v>8.561399999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.9702</v>
+        <v>-16.9985</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>3.119299999999999</v>
+        <v>13.1231</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.751600000000001</v>
+        <v>3.1739</v>
       </c>
       <c r="F8" t="n">
-        <v>7.8712</v>
+        <v>9.9488</v>
       </c>
       <c r="G8" t="n">
         <v>14.9537</v>
@@ -1078,13 +1078,13 @@
         <v>46.4156</v>
       </c>
       <c r="S8" t="n">
-        <v>-12.0811</v>
+        <v>-2.0776</v>
       </c>
       <c r="T8" t="n">
-        <v>-9.353200000000001</v>
+        <v>-1.4273</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.7281</v>
+        <v>-0.6500999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-4.2582</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>M. TOMIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0639</v>
+        <v>7.446199999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.926199999999999</v>
+        <v>7.087899999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>5.9898</v>
+        <v>0.3583</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8192000000000002</v>
+        <v>4.4129</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2173</v>
+        <v>-1.3401</v>
       </c>
       <c r="I9" t="n">
-        <v>3.036899999999999</v>
+        <v>5.7531</v>
       </c>
       <c r="J9" t="n">
-        <v>5.2871</v>
+        <v>8.940999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2853</v>
+        <v>1.366</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0021</v>
+        <v>7.5749</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.468</v>
+        <v>-4.5281</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.5029</v>
+        <v>-2.7061</v>
       </c>
       <c r="O9" t="n">
-        <v>2.0346</v>
+        <v>-1.8221</v>
       </c>
       <c r="P9" t="n">
-        <v>7.442</v>
+        <v>6.4628</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.9879</v>
+        <v>-2.3501</v>
       </c>
       <c r="R9" t="n">
-        <v>17.4303</v>
+        <v>8.812899999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-6.5394</v>
+        <v>0.2651</v>
       </c>
       <c r="T9" t="n">
-        <v>-4.2515</v>
+        <v>0.2216</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.2877</v>
+        <v>0.04340000000000006</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3419000000000002</v>
+        <v>-3.6948</v>
       </c>
       <c r="W9" t="n">
-        <v>5.0266</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.6848</v>
+        <v>-3.9702</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4037000000000011</v>
+        <v>6.245499999999998</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.7763</v>
+        <v>-1.14</v>
       </c>
       <c r="F10" t="n">
-        <v>8.180099999999999</v>
+        <v>7.3853</v>
       </c>
       <c r="G10" t="n">
-        <v>-11.1908</v>
+        <v>0.8192000000000002</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9162</v>
+        <v>-2.2173</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.2751</v>
+        <v>3.036899999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6578</v>
+        <v>5.2871</v>
       </c>
       <c r="K10" t="n">
-        <v>9.964500000000001</v>
+        <v>4.2853</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.3066</v>
+        <v>1.0021</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.8489</v>
+        <v>-4.468</v>
       </c>
       <c r="N10" t="n">
-        <v>-12.88</v>
+        <v>-6.5029</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.9685</v>
+        <v>2.0346</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.1336</v>
+        <v>7.442</v>
       </c>
       <c r="Q10" t="n">
-        <v>-32.119</v>
+        <v>-9.9879</v>
       </c>
       <c r="R10" t="n">
-        <v>28.9854</v>
+        <v>17.4303</v>
       </c>
       <c r="S10" t="n">
-        <v>16.9438</v>
+        <v>-2.3585</v>
       </c>
       <c r="T10" t="n">
-        <v>13.0764</v>
+        <v>-1.4658</v>
       </c>
       <c r="U10" t="n">
-        <v>3.8672</v>
+        <v>-0.8921999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.215399999999999</v>
+        <v>0.3419000000000002</v>
       </c>
       <c r="W10" t="n">
-        <v>6.6087</v>
+        <v>5.0266</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.824199999999999</v>
+        <v>-4.6848</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>R. REGUERA SOUTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1318999999999999</v>
+        <v>-0.202</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2098</v>
+        <v>-0.0555</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3417</v>
+        <v>-0.1465</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.9031</v>
+        <v>0.6360000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5636</v>
+        <v>-0.04630000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.3396</v>
+        <v>0.6821999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9707999999999998</v>
+        <v>0.0204</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6175</v>
+        <v>0.0204</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5885</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.9322</v>
+        <v>0.6155000000000002</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.1811</v>
+        <v>-0.06669999999999998</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.7511</v>
+        <v>0.6821999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.5046</v>
+        <v>0.1958</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.5135</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>9.009</v>
+        <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>7.832</v>
+        <v>-1.0338</v>
       </c>
       <c r="T11" t="n">
-        <v>7.9151</v>
+        <v>-0.0759</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08310000000000006</v>
+        <v>-0.9579</v>
       </c>
       <c r="V11" t="n">
-        <v>3.7073</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>5.3596</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. REGUERA SOUTO</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3845</v>
+        <v>-1.3507</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1578</v>
+        <v>1.0305</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2267</v>
+        <v>-2.3811</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6360000000000001</v>
+        <v>-0.3724999999999996</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.04630000000000001</v>
+        <v>-4.2692</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6821999999999999</v>
+        <v>3.8966</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0204</v>
+        <v>7.4214</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0204</v>
+        <v>0.6783999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.742599999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6155000000000002</v>
+        <v>-7.7937</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.06669999999999998</v>
+        <v>-4.9476</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6821999999999999</v>
+        <v>-2.8462</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1958</v>
+        <v>5.2878</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-7.833799999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1958</v>
+        <v>13.1217</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2163</v>
+        <v>-4.0057</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1782</v>
+        <v>-0.3239</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0381</v>
+        <v>-3.6816</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.2604</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.7674</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-4.027799999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>A. SOTO MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.619299999999999</v>
+        <v>-1.4215</v>
       </c>
       <c r="E13" t="n">
-        <v>2.524</v>
+        <v>-0.1634</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.143600000000001</v>
+        <v>-1.2583</v>
       </c>
       <c r="G13" t="n">
-        <v>5.586</v>
+        <v>-1.4076</v>
       </c>
       <c r="H13" t="n">
-        <v>2.213999999999998</v>
+        <v>-1.0541</v>
       </c>
       <c r="I13" t="n">
-        <v>3.372400000000001</v>
+        <v>-0.3535</v>
       </c>
       <c r="J13" t="n">
-        <v>36.9287</v>
+        <v>-0.5398000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>24.3657</v>
+        <v>-0.5802</v>
       </c>
       <c r="L13" t="n">
-        <v>12.5633</v>
+        <v>0.0404</v>
       </c>
       <c r="M13" t="n">
-        <v>-31.3425</v>
+        <v>-0.8678</v>
       </c>
       <c r="N13" t="n">
-        <v>-22.1516</v>
+        <v>-0.4739</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.1907</v>
+        <v>-0.3939000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>20.9557</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-31.3355</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>52.2912</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-19.7247</v>
+        <v>0.2612</v>
       </c>
       <c r="T13" t="n">
-        <v>-11.63</v>
+        <v>0.3764</v>
       </c>
       <c r="U13" t="n">
-        <v>-8.0945</v>
+        <v>-0.1151</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.437100000000001</v>
+        <v>-0.2754</v>
       </c>
       <c r="W13" t="n">
-        <v>8.561399999999999</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.9985</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.8213</v>
+        <v>-1.7946</v>
       </c>
       <c r="E14" t="n">
         <v>-2.2843</v>
       </c>
       <c r="F14" t="n">
-        <v>0.463</v>
+        <v>0.4897</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6592</v>
@@ -1546,13 +1546,13 @@
         <v>0.3916</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2198</v>
+        <v>-0.1931</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V14" t="n">
         <v>0.6659</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SOTO MARTINEZ</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1158</v>
+        <v>-2.4653</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7774000000000001</v>
+        <v>-4.058800000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3384</v>
+        <v>1.5935</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4076</v>
+        <v>-6.9031</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0541</v>
+        <v>-1.5636</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3535</v>
+        <v>-5.3396</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5398000000000001</v>
+        <v>-0.9707999999999998</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5802</v>
+        <v>1.6175</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0404</v>
+        <v>-2.5885</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8678</v>
+        <v>-5.9322</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4739</v>
+        <v>-3.1811</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3939000000000001</v>
+        <v>-2.7511</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-4.5046</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-13.5135</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>9.009</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4330000000000001</v>
+        <v>5.2348</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2376</v>
+        <v>5.066199999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1954</v>
+        <v>0.1686</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2754</v>
+        <v>3.7073</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>5.3596</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2754</v>
+        <v>-1.6522</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.591</v>
+        <v>-3.8916</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0492</v>
+        <v>-5.3227</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5418</v>
+        <v>1.4316</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3724999999999996</v>
+        <v>-3.133</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.2692</v>
+        <v>-1.4716</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8966</v>
+        <v>-1.6614</v>
       </c>
       <c r="J16" t="n">
-        <v>7.4214</v>
+        <v>14.1773</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6783999999999999</v>
+        <v>10.9909</v>
       </c>
       <c r="L16" t="n">
-        <v>6.742599999999999</v>
+        <v>3.1861</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.7937</v>
+        <v>-17.3102</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.9476</v>
+        <v>-12.4627</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.8462</v>
+        <v>-4.8479</v>
       </c>
       <c r="P16" t="n">
-        <v>5.2878</v>
+        <v>4.8963</v>
       </c>
       <c r="Q16" t="n">
-        <v>-7.833799999999999</v>
+        <v>-28.7895</v>
       </c>
       <c r="R16" t="n">
-        <v>13.1217</v>
+        <v>33.6857</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.2459</v>
+        <v>4.7223</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.4037</v>
+        <v>4.9994</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.8421</v>
+        <v>-0.2764</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.2604</v>
+        <v>-10.3771</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7674</v>
+        <v>4.290699999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.027799999999999</v>
+        <v>-14.6678</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.988999999999999</v>
+        <v>-8.7844</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0682</v>
+        <v>-15.4713</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.921</v>
+        <v>6.6876</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.133</v>
+        <v>-11.1908</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4716</v>
+        <v>-2.9162</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6614</v>
+        <v>-8.2751</v>
       </c>
       <c r="J17" t="n">
-        <v>14.1773</v>
+        <v>4.6578</v>
       </c>
       <c r="K17" t="n">
-        <v>10.9909</v>
+        <v>9.964500000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1861</v>
+        <v>-5.3066</v>
       </c>
       <c r="M17" t="n">
-        <v>-17.3102</v>
+        <v>-15.8489</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.4627</v>
+        <v>-12.88</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.8479</v>
+        <v>-2.9685</v>
       </c>
       <c r="P17" t="n">
-        <v>4.8963</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q17" t="n">
-        <v>-28.7895</v>
+        <v>-32.119</v>
       </c>
       <c r="R17" t="n">
-        <v>33.6857</v>
+        <v>28.9854</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6252</v>
+        <v>7.7556</v>
       </c>
       <c r="T17" t="n">
-        <v>7.254099999999999</v>
+        <v>5.3815</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.629</v>
+        <v>2.3742</v>
       </c>
       <c r="V17" t="n">
-        <v>-10.3771</v>
+        <v>-2.215399999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>4.290699999999999</v>
+        <v>6.6087</v>
       </c>
       <c r="X17" t="n">
-        <v>-14.6678</v>
+        <v>-8.824199999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.7704</v>
+        <v>-11.7019</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.3021</v>
+        <v>-9.311500000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4682</v>
+        <v>-2.3905</v>
       </c>
       <c r="G18" t="n">
         <v>-4.0854</v>
@@ -1858,13 +1858,13 @@
         <v>20.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-8.5992</v>
+        <v>-3.5312</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.8506</v>
+        <v>-0.8601</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.7488</v>
+        <v>-2.6708</v>
       </c>
       <c r="V18" t="n">
         <v>-9.7653</v>
@@ -1891,19 +1891,19 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>198.1488</v>
+        <v>225.0949</v>
       </c>
       <c r="E19" t="n">
-        <v>94.2574</v>
+        <v>103.4652</v>
       </c>
       <c r="F19" t="n">
-        <v>103.8914</v>
+        <v>121.6305</v>
       </c>
       <c r="G19" t="n">
         <v>98.56229999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>44.3134</v>
+        <v>44.31339999999999</v>
       </c>
       <c r="I19" t="n">
         <v>54.24939999999999</v>
@@ -1915,7 +1915,7 @@
         <v>201.6257</v>
       </c>
       <c r="L19" t="n">
-        <v>91.6164</v>
+        <v>91.61639999999998</v>
       </c>
       <c r="M19" t="n">
         <v>-194.6807</v>
@@ -1924,10 +1924,10 @@
         <v>-157.3125</v>
       </c>
       <c r="O19" t="n">
-        <v>-37.36810000000001</v>
+        <v>-37.3681</v>
       </c>
       <c r="P19" t="n">
-        <v>62.66990000000001</v>
+        <v>62.6699</v>
       </c>
       <c r="Q19" t="n">
         <v>-394.6319999999999</v>
@@ -1936,13 +1936,13 @@
         <v>457.3029</v>
       </c>
       <c r="S19" t="n">
-        <v>10.5404</v>
+        <v>37.4834</v>
       </c>
       <c r="T19" t="n">
-        <v>22.825</v>
+        <v>32.03189999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-12.2851</v>
+        <v>5.453600000000002</v>
       </c>
       <c r="V19" t="n">
         <v>26.37470000000001</v>
